--- a/output/pdf_financials_xlsx/BLAB.xlsx
+++ b/output/pdf_financials_xlsx/BLAB.xlsx
@@ -1918,13 +1918,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0.157101</v>
+        <v>1.427843</v>
       </c>
       <c r="C92" s="3" t="n">
         <v>3.409434</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>3.409434</v>
+        <v>3.458948</v>
       </c>
     </row>
     <row r="93">
@@ -3658,7 +3658,11 @@
           <t>Warrant reserve 13</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E33" t="inlineStr">
         <is>
           <t>-</t>
@@ -4414,7 +4418,11 @@
           <t>Warrant reserve 13</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E57" s="5" t="n">
         <v>1.270742</v>
       </c>

--- a/output/pdf_financials_xlsx/BLAB.xlsx
+++ b/output/pdf_financials_xlsx/BLAB.xlsx
@@ -982,13 +982,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>2.598273</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>1.322584</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>7.848756</v>
       </c>
     </row>
     <row r="35">
@@ -1014,13 +1014,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>2.598273</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>1.322584</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>7.848756</v>
       </c>
     </row>
     <row r="37">
@@ -1206,13 +1206,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>2.621714</v>
+        <v>0.023441</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1.335351</v>
+        <v>0.012767</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>9.697264000000001</v>
+        <v>1.848508</v>
       </c>
     </row>
     <row r="49">
@@ -2423,13 +2423,13 @@
         </is>
       </c>
       <c r="B124" s="3" t="n">
-        <v>0</v>
+        <v>-0.073542</v>
       </c>
       <c r="C124" s="3" t="n">
-        <v>0</v>
+        <v>-0.08645</v>
       </c>
       <c r="D124" s="3" t="n">
-        <v>0</v>
+        <v>-0.09095300000000001</v>
       </c>
     </row>
     <row r="125">
@@ -2439,13 +2439,13 @@
         </is>
       </c>
       <c r="B125" s="3" t="n">
-        <v>0</v>
+        <v>-0.073542</v>
       </c>
       <c r="C125" s="3" t="n">
-        <v>0</v>
+        <v>-0.08645</v>
       </c>
       <c r="D125" s="3" t="n">
-        <v>0</v>
+        <v>-0.09095300000000001</v>
       </c>
     </row>
     <row r="126">
@@ -2741,7 +2741,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E4" s="5" t="n">
@@ -5615,7 +5615,11 @@
           <t>Lease payments 8</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr"/>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E96" t="inlineStr">
         <is>
           <t>-</t>
@@ -6570,7 +6574,11 @@
           <t>Lease payments 8</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr"/>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E127" s="5" t="n">
         <v>-0.073542</v>
       </c>

--- a/output/pdf_financials_xlsx/BLAB.xlsx
+++ b/output/pdf_financials_xlsx/BLAB.xlsx
@@ -752,10 +752,10 @@
         <v>5.838186</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>-4.398484</v>
+        <v>-6.116163</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>7.50677</v>
+        <v>-4.560608</v>
       </c>
     </row>
     <row r="21">
@@ -768,10 +768,10 @@
         <v>0</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>0</v>
+        <v>1.717679</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>0</v>
+        <v>12.067378</v>
       </c>
     </row>
     <row r="22">
@@ -1388,10 +1388,10 @@
         </is>
       </c>
       <c r="B59" s="3" t="n">
-        <v>17.607288</v>
+        <v>0</v>
       </c>
       <c r="C59" s="3" t="n">
-        <v>18.080656</v>
+        <v>0</v>
       </c>
       <c r="D59" s="3" t="n">
         <v>0</v>
@@ -1420,10 +1420,10 @@
         </is>
       </c>
       <c r="B61" s="3" t="n">
-        <v>1.269809</v>
+        <v>18.877097</v>
       </c>
       <c r="C61" s="3" t="n">
-        <v>0</v>
+        <v>0.731204</v>
       </c>
       <c r="D61" s="3" t="n">
         <v>1.542147</v>
@@ -2197,13 +2197,13 @@
         </is>
       </c>
       <c r="B110" s="3" t="n">
-        <v>0</v>
+        <v>0.037444</v>
       </c>
       <c r="C110" s="3" t="n">
-        <v>0</v>
+        <v>0.001964</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>0</v>
+        <v>0.071802</v>
       </c>
     </row>
     <row r="111">
@@ -2213,10 +2213,10 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.055308</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.134871</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>0</v>
@@ -2293,10 +2293,10 @@
         </is>
       </c>
       <c r="B116" s="3" t="n">
-        <v>0</v>
+        <v>-0.286992</v>
       </c>
       <c r="C116" s="3" t="n">
-        <v>0</v>
+        <v>-0.202603</v>
       </c>
       <c r="D116" s="3" t="n">
         <v>0</v>
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.055308</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.134871</v>
       </c>
       <c r="D134" s="3" t="n">
         <v>0</v>
@@ -2607,10 +2607,10 @@
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>2.008374</v>
+        <v>1.953066</v>
       </c>
       <c r="C135" s="3" t="n">
-        <v>2.091656</v>
+        <v>1.956785</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>-2.619606</v>
@@ -3914,7 +3914,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>OtherIntangibleAssets</t>
+          <t>GoodwillAndOtherIntangibleAssets</t>
         </is>
       </c>
       <c r="E41" s="5" t="n">
@@ -4856,7 +4856,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr"/>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E71" t="inlineStr">
         <is>
           <t>-</t>
@@ -5956,7 +5960,11 @@
           <t>Net Income (loss)</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr"/>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E107" s="5" t="n">
         <v>5.838186</v>
       </c>
@@ -6047,7 +6055,11 @@
           <t>Accretion expense 7, 13</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr"/>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E110" s="5" t="n">
         <v>0.037444</v>
       </c>
@@ -6425,7 +6437,11 @@
           <t>Acquisition of intangible assets 5</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr"/>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E122" s="5" t="n">
         <v>-0.286992</v>
       </c>
@@ -6454,7 +6470,11 @@
           <t>Acquisition of equipment 4</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr"/>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E123" s="5" t="n">
         <v>-0.055308</v>
       </c>
@@ -7597,7 +7617,11 @@
           <t>Deferred income tax recovery 10</t>
         </is>
       </c>
-      <c r="D160" t="inlineStr"/>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E160" t="inlineStr">
         <is>
           <t>-</t>
@@ -7663,7 +7687,11 @@
           <t>Net loss from continuing operations</t>
         </is>
       </c>
-      <c r="D162" t="inlineStr"/>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E162" t="inlineStr">
         <is>
           <t>-</t>
@@ -7692,7 +7720,11 @@
           <t>Net income from discontinued operations 6(a)</t>
         </is>
       </c>
-      <c r="D163" t="inlineStr"/>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E163" t="inlineStr">
         <is>
           <t>-</t>
